--- a/tracking/lab_information.xlsx
+++ b/tracking/lab_information.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erinbuchanan/GitHub/Research/2_projects/Neel-2016/tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A2438F-308B-5E4C-B89F-416D36383065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344BD920-43CD-B34E-8C29-B4AAAB34578A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{6DE37660-5408-1E44-BA29-F8DCB601BB2B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
   <si>
     <t>CREP Number</t>
   </si>
@@ -155,31 +155,16 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Not Downloaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSF connected to google drive, which is not available. </t>
-  </si>
-  <si>
     <t>Not Completed</t>
   </si>
   <si>
     <t>Australia</t>
   </si>
   <si>
-    <t>Raw Data Not Incuded</t>
-  </si>
-  <si>
     <t>Poland</t>
   </si>
   <si>
     <t>Türkiye</t>
-  </si>
-  <si>
-    <t>Output document only, emailed Amelie</t>
-  </si>
-  <si>
-    <t>OSF Link Broken, emailed Amelie</t>
   </si>
   <si>
     <r>
@@ -718,9 +703,7 @@
       <c r="D4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="3"/>
       <c r="G4" s="8"/>
     </row>
@@ -729,7 +712,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>35</v>
@@ -742,7 +725,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>35</v>
@@ -755,10 +738,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="6"/>
@@ -771,7 +754,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>35</v>
@@ -800,7 +783,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>35</v>
@@ -816,13 +799,10 @@
         <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="F11" s="5"/>
     </row>
@@ -831,10 +811,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>35</v>
@@ -847,10 +827,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="9"/>
@@ -863,13 +843,10 @@
         <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F14" s="5"/>
     </row>
@@ -897,13 +874,13 @@
         <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="8"/>
@@ -945,7 +922,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>35</v>
